--- a/Nhom01/SE_9/SE_9_Nhom01_Epics.xlsx
+++ b/Nhom01/SE_9/SE_9_Nhom01_Epics.xlsx
@@ -522,7 +522,7 @@
       </c>
       <c r="B5" s="8" t="inlineStr">
         <is>
-          <t>Acceptance criteria theo rubric môn học</t>
+          <t>Tiêu chí nghiệm thu theo yêu cầu môn học</t>
         </is>
       </c>
       <c r="C5" s="8" t="inlineStr">
@@ -559,7 +559,7 @@
       </c>
       <c r="B6" s="5" t="inlineStr">
         <is>
-          <t>At least 5 epics, each a business outcome that can span more than one sprint.</t>
+          <t>Có ít nhất 5 nhóm nghiệp vụ; mỗi nhóm nghiệp vụ thể hiện một kết quả nghiệp vụ và có thể kéo dài hơn một đợt phát triển.</t>
         </is>
       </c>
       <c r="C6" s="5" t="inlineStr">
@@ -574,7 +574,7 @@
       </c>
       <c r="E6" s="5" t="inlineStr">
         <is>
-          <t>Rows 4–8</t>
+          <t>EP-001–EP-005</t>
         </is>
       </c>
       <c r="F6" s="5" t="inlineStr">
@@ -596,7 +596,7 @@
       </c>
       <c r="B7" s="5" t="inlineStr">
         <is>
-          <t>Each has ID, title, owner, description and business value.</t>
+          <t>Mỗi nhóm nghiệp vụ có mã, tên, người phụ trách, mô tả và giá trị nghiệp vụ.</t>
         </is>
       </c>
       <c r="C7" s="5" t="inlineStr">
@@ -611,7 +611,7 @@
       </c>
       <c r="E7" s="5" t="inlineStr">
         <is>
-          <t>Rows 4–8, A:E</t>
+          <t>EP-001–EP-005</t>
         </is>
       </c>
       <c r="F7" s="5" t="inlineStr">
@@ -633,7 +633,7 @@
       </c>
       <c r="B8" s="5" t="inlineStr">
         <is>
-          <t>Checkable if/then acceptance criteria cover the epic and its connections to other epics.</t>
+          <t>Tiêu chí nghiệm thu của nhóm nghiệp vụ là các điều kiện và kết quả kiểm tra được; bao quát toàn nhóm nghiệp vụ, kể cả kết nối với nhóm nghiệp vụ khác.</t>
         </is>
       </c>
       <c r="C8" s="5" t="inlineStr">
@@ -648,7 +648,7 @@
       </c>
       <c r="E8" s="5" t="inlineStr">
         <is>
-          <t>Rows 4–8</t>
+          <t>EP-001–EP-005</t>
         </is>
       </c>
       <c r="F8" s="5" t="inlineStr">
@@ -670,7 +670,7 @@
       </c>
       <c r="B9" s="5" t="inlineStr">
         <is>
-          <t>Where needed, criteria cover security, authorization, performance, usability and compliance.</t>
+          <t>Khi cần, tiêu chí của nhóm nghiệp vụ bao gồm bảo mật, phân quyền, hiệu năng, tính dễ sử dụng và tuân thủ.</t>
         </is>
       </c>
       <c r="C9" s="5" t="inlineStr">
@@ -685,7 +685,7 @@
       </c>
       <c r="E9" s="5" t="inlineStr">
         <is>
-          <t>Rows 4–8; đối chiếu NFR</t>
+          <t>EP-001–EP-005; NFR-001–NFR-010</t>
         </is>
       </c>
       <c r="F9" s="5" t="inlineStr">
@@ -707,7 +707,7 @@
       </c>
       <c r="B10" s="5" t="inlineStr">
         <is>
-          <t>Dependencies state which epic is needed and why; constraints and assumptions are documented.</t>
+          <t>Quan hệ phụ thuộc nêu nhóm nghiệp vụ nào cần có trước và lý do; các ràng buộc và giả định được ghi lại.</t>
         </is>
       </c>
       <c r="C10" s="5" t="inlineStr">
@@ -722,7 +722,7 @@
       </c>
       <c r="E10" s="5" t="inlineStr">
         <is>
-          <t>Rows 4–8</t>
+          <t>EP-001–EP-005</t>
         </is>
       </c>
       <c r="F10" s="5" t="inlineStr">
@@ -744,7 +744,7 @@
       </c>
       <c r="B11" s="5" t="inlineStr">
         <is>
-          <t>Priority and estimate are present; child story IDs exist in the User Story file.</t>
+          <t>Mỗi nhóm nghiệp vụ có mức ưu tiên và ước lượng; mã các câu chuyện người dùng con tồn tại trong tệp câu chuyện người dùng.</t>
         </is>
       </c>
       <c r="C11" s="5" t="inlineStr">
@@ -759,7 +759,7 @@
       </c>
       <c r="E11" s="5" t="inlineStr">
         <is>
-          <t>Rows 4–8; UserStory rows 2–17</t>
+          <t>EP-001–EP-005; US-001–US-016</t>
         </is>
       </c>
       <c r="F11" s="5" t="inlineStr">
